--- a/AAII_Financials/Quarterly/CURB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CURB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>CURB</t>
   </si>
@@ -656,99 +656,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E8" s="3">
         <v>29800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>28100</v>
       </c>
       <c r="F8" s="3">
         <v>28100</v>
       </c>
       <c r="G8" s="3">
+        <v>28100</v>
+      </c>
+      <c r="H8" s="3">
+        <v>25500</v>
+      </c>
+      <c r="I8" s="3">
         <v>24200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>22000</v>
       </c>
-      <c r="I8" s="3">
-        <v>22000</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E9" s="3">
         <v>6900</v>
-      </c>
-      <c r="E9" s="3">
-        <v>6000</v>
       </c>
       <c r="F9" s="3">
         <v>6000</v>
@@ -757,48 +762,54 @@
         <v>6000</v>
       </c>
       <c r="H9" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I9" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J9" s="3">
         <v>5200</v>
       </c>
-      <c r="I9" s="3">
-        <v>5200</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E10" s="3">
         <v>22900</v>
-      </c>
-      <c r="E10" s="3">
-        <v>22100</v>
       </c>
       <c r="F10" s="3">
         <v>22100</v>
       </c>
       <c r="G10" s="3">
+        <v>22100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>19900</v>
+      </c>
+      <c r="I10" s="3">
         <v>18300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>16800</v>
       </c>
-      <c r="I10" s="3">
-        <v>16800</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +821,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,8 +851,11 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,66 +883,75 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E14" s="3">
         <v>23600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I14" s="3">
         <v>-400</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E15" s="3">
         <v>11100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>9300</v>
       </c>
       <c r="F15" s="3">
         <v>9300</v>
       </c>
       <c r="G15" s="3">
+        <v>9300</v>
+      </c>
+      <c r="H15" s="3">
+        <v>8800</v>
+      </c>
+      <c r="I15" s="3">
         <v>8000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>7600</v>
       </c>
-      <c r="I15" s="3">
-        <v>7600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,66 +960,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E17" s="3">
         <v>21500</v>
-      </c>
-      <c r="E17" s="3">
-        <v>17200</v>
       </c>
       <c r="F17" s="3">
         <v>17200</v>
       </c>
       <c r="G17" s="3">
+        <v>17200</v>
+      </c>
+      <c r="H17" s="3">
+        <v>15800</v>
+      </c>
+      <c r="I17" s="3">
         <v>15100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>13900</v>
       </c>
-      <c r="I17" s="3">
-        <v>13900</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E18" s="3">
         <v>8200</v>
-      </c>
-      <c r="E18" s="3">
-        <v>10900</v>
       </c>
       <c r="F18" s="3">
         <v>10900</v>
       </c>
       <c r="G18" s="3">
+        <v>10900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>9700</v>
+      </c>
+      <c r="I18" s="3">
         <v>9200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>8000</v>
       </c>
-      <c r="I18" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,80 +1038,87 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
-        <v>3600</v>
+      <c r="D20" s="3">
+        <v>-31100</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
         <v>3600</v>
       </c>
       <c r="G20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
-        <v>300</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E21" s="3">
         <v>19300</v>
-      </c>
-      <c r="E21" s="3">
-        <v>16600</v>
       </c>
       <c r="F21" s="3">
         <v>16600</v>
       </c>
       <c r="G21" s="3">
+        <v>16600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>19500</v>
+      </c>
+      <c r="I21" s="3">
         <v>16800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>15300</v>
       </c>
-      <c r="I21" s="3">
-        <v>15300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3">
-        <v>200</v>
+      <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>200</v>
       </c>
       <c r="G22" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H22" s="3">
         <v>400</v>
@@ -1088,48 +1126,54 @@
       <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>400</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15400</v>
-      </c>
-      <c r="E23" s="3">
-        <v>7100</v>
       </c>
       <c r="F23" s="3">
         <v>7100</v>
       </c>
       <c r="G23" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H23" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I23" s="3">
         <v>8800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>7300</v>
       </c>
-      <c r="I23" s="3">
-        <v>7300</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -1152,8 +1196,11 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,66 +1228,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15400</v>
-      </c>
-      <c r="E26" s="3">
-        <v>7100</v>
       </c>
       <c r="F26" s="3">
         <v>7100</v>
       </c>
       <c r="G26" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H26" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I26" s="3">
         <v>8800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>7300</v>
       </c>
-      <c r="I26" s="3">
-        <v>7300</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-15400</v>
-      </c>
-      <c r="E27" s="3">
-        <v>7100</v>
       </c>
       <c r="F27" s="3">
         <v>7100</v>
       </c>
       <c r="G27" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H27" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I27" s="3">
         <v>8800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>7300</v>
       </c>
-      <c r="I27" s="3">
-        <v>7300</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1324,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1356,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1388,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,66 +1420,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-3600</v>
+      <c r="D32" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
         <v>-3600</v>
       </c>
       <c r="G32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15400</v>
-      </c>
-      <c r="E33" s="3">
-        <v>7100</v>
       </c>
       <c r="F33" s="3">
         <v>7100</v>
       </c>
       <c r="G33" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H33" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I33" s="3">
         <v>8800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>7300</v>
       </c>
-      <c r="I33" s="3">
-        <v>7300</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,71 +1516,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15400</v>
-      </c>
-      <c r="E35" s="3">
-        <v>7100</v>
       </c>
       <c r="F35" s="3">
         <v>7100</v>
       </c>
       <c r="G35" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H35" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I35" s="3">
         <v>8800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>7300</v>
       </c>
-      <c r="I35" s="3">
-        <v>7300</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1601,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,25 +1615,26 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>626400</v>
+      </c>
+      <c r="E41" s="3">
         <v>2500</v>
-      </c>
-      <c r="E41" s="3">
-        <v>1500</v>
       </c>
       <c r="F41" s="3">
         <v>1500</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
+      <c r="G41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H41" s="3">
+        <v>600</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1560,8 +1645,11 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1589,25 +1677,28 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E43" s="3">
         <v>12700</v>
-      </c>
-      <c r="E43" s="3">
-        <v>11500</v>
       </c>
       <c r="F43" s="3">
         <v>11500</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="G43" s="3">
+        <v>11500</v>
+      </c>
+      <c r="H43" s="3">
+        <v>11500</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1618,8 +1709,11 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1647,25 +1741,28 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6500</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>400</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1676,25 +1773,28 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>682100</v>
+      </c>
+      <c r="E46" s="3">
         <v>21700</v>
-      </c>
-      <c r="E46" s="3">
-        <v>13100</v>
       </c>
       <c r="F46" s="3">
         <v>13100</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+      <c r="G46" s="3">
+        <v>13100</v>
+      </c>
+      <c r="H46" s="3">
+        <v>12700</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1705,8 +1805,11 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1734,25 +1837,28 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1262200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1075800</v>
-      </c>
-      <c r="E48" s="3">
-        <v>938500</v>
       </c>
       <c r="F48" s="3">
         <v>938500</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+      <c r="G48" s="3">
+        <v>938500</v>
+      </c>
+      <c r="H48" s="3">
+        <v>874600</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1763,28 +1869,31 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>82700</v>
+      </c>
+      <c r="E49" s="3">
         <v>62900</v>
-      </c>
-      <c r="E49" s="3">
-        <v>50700</v>
       </c>
       <c r="F49" s="3">
         <v>50700</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="G49" s="3">
+        <v>50700</v>
+      </c>
+      <c r="H49" s="3">
+        <v>34300</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -1792,8 +1901,11 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +1933,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,22 +1965,25 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E52" s="3">
         <v>6600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2300</v>
       </c>
       <c r="F52" s="3">
         <v>2300</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+      <c r="G52" s="3">
+        <v>2300</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1879,8 +1997,11 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,25 +2029,28 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2033100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1167100</v>
-      </c>
-      <c r="E54" s="3">
-        <v>1004700</v>
       </c>
       <c r="F54" s="3">
         <v>1004700</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+      <c r="G54" s="3">
+        <v>1004700</v>
+      </c>
+      <c r="H54" s="3">
+        <v>921600</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -1937,8 +2061,11 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2077,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,25 +2091,26 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E57" s="3">
         <v>19600</v>
-      </c>
-      <c r="E57" s="3">
-        <v>17200</v>
       </c>
       <c r="F57" s="3">
         <v>17200</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+      <c r="G57" s="3">
+        <v>17200</v>
+      </c>
+      <c r="H57" s="3">
+        <v>12000</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -1992,8 +2121,11 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2006,14 +2138,14 @@
       <c r="F58" s="3">
         <v>0</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2021,13 +2153,16 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>26700</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>3</v>
@@ -2050,25 +2185,28 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E60" s="3">
         <v>19600</v>
-      </c>
-      <c r="E60" s="3">
-        <v>17200</v>
       </c>
       <c r="F60" s="3">
         <v>17200</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+      <c r="G60" s="3">
+        <v>17200</v>
+      </c>
+      <c r="H60" s="3">
+        <v>12000</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2079,8 +2217,11 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2097,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>25800</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2108,25 +2249,28 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E62" s="3">
         <v>30500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>22000</v>
       </c>
       <c r="F62" s="3">
         <v>22000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="G62" s="3">
+        <v>22000</v>
+      </c>
+      <c r="H62" s="3">
+        <v>21200</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2137,8 +2281,11 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2313,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2345,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,25 +2377,28 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>90500</v>
+      </c>
+      <c r="E66" s="3">
         <v>50000</v>
-      </c>
-      <c r="E66" s="3">
-        <v>39100</v>
       </c>
       <c r="F66" s="3">
         <v>39100</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+      <c r="G66" s="3">
+        <v>39100</v>
+      </c>
+      <c r="H66" s="3">
+        <v>59000</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2253,8 +2409,11 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2425,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2455,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2487,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2519,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,8 +2551,11 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2411,8 +2583,11 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2615,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2647,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,28 +2679,31 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1941800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1117000</v>
-      </c>
-      <c r="E76" s="3">
-        <v>965500</v>
       </c>
       <c r="F76" s="3">
         <v>965500</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3">
-        <v>691800</v>
+      <c r="G76" s="3">
+        <v>965500</v>
+      </c>
+      <c r="H76" s="3">
+        <v>862600</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -2527,8 +2711,11 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,71 +2743,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15400</v>
-      </c>
-      <c r="E81" s="3">
-        <v>7100</v>
       </c>
       <c r="F81" s="3">
         <v>7100</v>
       </c>
       <c r="G81" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H81" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I81" s="3">
         <v>8800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>7300</v>
       </c>
-      <c r="I81" s="3">
-        <v>7300</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,23 +2828,24 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F83" s="3">
         <v>7600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>7600</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2661,8 +2858,11 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +2890,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +2922,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +2954,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +2986,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,37 +3018,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7100</v>
-      </c>
-      <c r="E89" s="3">
-        <v>16200</v>
       </c>
       <c r="F89" s="3">
         <v>16200</v>
       </c>
       <c r="G89" s="3">
+        <v>16200</v>
+      </c>
+      <c r="H89" s="3">
+        <v>10300</v>
+      </c>
+      <c r="I89" s="3">
         <v>17400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>15800</v>
       </c>
-      <c r="I89" s="3">
-        <v>15800</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,8 +3066,9 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2877,8 +3096,11 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3128,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,37 +3160,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-202700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-153800</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-40400</v>
       </c>
       <c r="F94" s="3">
         <v>-40400</v>
       </c>
       <c r="G94" s="3">
+        <v>-40400</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="I94" s="3">
         <v>-31900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-43600</v>
       </c>
-      <c r="I94" s="3">
-        <v>-43600</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,8 +3208,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3006,8 +3238,11 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3270,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3302,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,37 +3334,43 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>797600</v>
+      </c>
+      <c r="E100" s="3">
         <v>161900</v>
-      </c>
-      <c r="E100" s="3">
-        <v>24700</v>
       </c>
       <c r="F100" s="3">
         <v>24700</v>
       </c>
       <c r="G100" s="3">
+        <v>24700</v>
+      </c>
+      <c r="H100" s="3">
+        <v>56300</v>
+      </c>
+      <c r="I100" s="3">
         <v>14600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>28000</v>
       </c>
-      <c r="I100" s="3">
-        <v>28000</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3151,33 +3398,39 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>623900</v>
+      </c>
+      <c r="E102" s="3">
         <v>1000</v>
-      </c>
-      <c r="E102" s="3">
-        <v>400</v>
       </c>
       <c r="F102" s="3">
         <v>400</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
-        <v>200</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CURB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CURB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>CURB</t>
   </si>
@@ -656,43 +656,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45473</v>
       </c>
       <c r="G7" s="2">
         <v>45382</v>
@@ -706,28 +706,31 @@
       <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
+      <c r="K7" s="2">
+        <v>45107</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E8" s="3">
         <v>34900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>29800</v>
       </c>
-      <c r="F8" s="3">
-        <v>28100</v>
-      </c>
       <c r="G8" s="3">
-        <v>28100</v>
+        <v>28000</v>
       </c>
       <c r="H8" s="3">
         <v>25500</v>
@@ -738,25 +741,28 @@
       <c r="J8" s="3">
         <v>22000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
+      <c r="K8" s="3">
+        <v>22000</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E9" s="3">
         <v>8800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6900</v>
-      </c>
-      <c r="F9" s="3">
-        <v>6000</v>
       </c>
       <c r="G9" s="3">
         <v>6000</v>
@@ -770,25 +776,28 @@
       <c r="J9" s="3">
         <v>5200</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
+      <c r="K9" s="3">
+        <v>5200</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E10" s="3">
         <v>26200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>22900</v>
-      </c>
-      <c r="F10" s="3">
-        <v>22100</v>
       </c>
       <c r="G10" s="3">
         <v>22100</v>
@@ -802,14 +811,17 @@
       <c r="J10" s="3">
         <v>16800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
+      <c r="K10" s="3">
+        <v>16800</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -822,8 +834,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -854,8 +867,11 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -886,19 +902,22 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>30800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>23600</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -918,22 +937,25 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E15" s="3">
         <v>12200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11100</v>
       </c>
-      <c r="F15" s="3">
-        <v>9300</v>
-      </c>
       <c r="G15" s="3">
-        <v>9300</v>
+        <v>9200</v>
       </c>
       <c r="H15" s="3">
         <v>8800</v>
@@ -945,13 +967,16 @@
         <v>7600</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -961,22 +986,23 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E17" s="3">
         <v>31100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21500</v>
       </c>
-      <c r="F17" s="3">
-        <v>17200</v>
-      </c>
       <c r="G17" s="3">
-        <v>17200</v>
+        <v>16700</v>
       </c>
       <c r="H17" s="3">
         <v>15800</v>
@@ -987,28 +1013,31 @@
       <c r="J17" s="3">
         <v>13900</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
+      <c r="K17" s="3">
+        <v>13900</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E18" s="3">
         <v>3800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8200</v>
       </c>
-      <c r="F18" s="3">
-        <v>10900</v>
-      </c>
       <c r="G18" s="3">
-        <v>10900</v>
+        <v>11300</v>
       </c>
       <c r="H18" s="3">
         <v>9700</v>
@@ -1019,14 +1048,17 @@
       <c r="J18" s="3">
         <v>8000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
+      <c r="K18" s="3">
+        <v>8000</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1039,22 +1071,23 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-31100</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
-        <v>3600</v>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="H20" s="3">
         <v>-1000</v>
@@ -1065,28 +1098,31 @@
       <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>300</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E21" s="3">
         <v>47100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19300</v>
       </c>
-      <c r="F21" s="3">
-        <v>16600</v>
-      </c>
       <c r="G21" s="3">
-        <v>16600</v>
+        <v>17500</v>
       </c>
       <c r="H21" s="3">
         <v>19500</v>
@@ -1098,27 +1134,30 @@
         <v>15300</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>15300</v>
       </c>
       <c r="L21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
-        <v>200</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H22" s="3">
         <v>400</v>
@@ -1129,28 +1168,31 @@
       <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>400</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E23" s="3">
         <v>11500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15400</v>
       </c>
-      <c r="F23" s="3">
-        <v>7100</v>
-      </c>
       <c r="G23" s="3">
-        <v>7100</v>
+        <v>8000</v>
       </c>
       <c r="H23" s="3">
         <v>7600</v>
@@ -1161,22 +1203,25 @@
       <c r="J23" s="3">
         <v>7300</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
+      <c r="K23" s="3">
+        <v>7300</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1199,8 +1244,11 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1231,22 +1279,25 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E26" s="3">
         <v>11500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15400</v>
       </c>
-      <c r="F26" s="3">
-        <v>7100</v>
-      </c>
       <c r="G26" s="3">
-        <v>7100</v>
+        <v>8000</v>
       </c>
       <c r="H26" s="3">
         <v>7600</v>
@@ -1257,28 +1308,31 @@
       <c r="J26" s="3">
         <v>7300</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
+      <c r="K26" s="3">
+        <v>7300</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E27" s="3">
         <v>11200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15400</v>
       </c>
-      <c r="F27" s="3">
-        <v>7100</v>
-      </c>
       <c r="G27" s="3">
-        <v>7100</v>
+        <v>8000</v>
       </c>
       <c r="H27" s="3">
         <v>7600</v>
@@ -1289,14 +1343,17 @@
       <c r="J27" s="3">
         <v>7300</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
+      <c r="K27" s="3">
+        <v>7300</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1327,8 +1384,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1359,8 +1419,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1391,8 +1454,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1423,22 +1489,25 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
         <v>31100</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-3600</v>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3">
-        <v>-3600</v>
+        <v>-3100</v>
       </c>
       <c r="H32" s="3">
         <v>1000</v>
@@ -1449,28 +1518,31 @@
       <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>-300</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E33" s="3">
         <v>11500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15400</v>
       </c>
-      <c r="F33" s="3">
-        <v>7100</v>
-      </c>
       <c r="G33" s="3">
-        <v>7100</v>
+        <v>8000</v>
       </c>
       <c r="H33" s="3">
         <v>7600</v>
@@ -1481,14 +1553,17 @@
       <c r="J33" s="3">
         <v>7300</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
+      <c r="K33" s="3">
+        <v>7300</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1519,22 +1594,25 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E35" s="3">
         <v>11500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15400</v>
       </c>
-      <c r="F35" s="3">
-        <v>7100</v>
-      </c>
       <c r="G35" s="3">
-        <v>7100</v>
+        <v>8000</v>
       </c>
       <c r="H35" s="3">
         <v>7600</v>
@@ -1545,30 +1623,33 @@
       <c r="J35" s="3">
         <v>7300</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
+      <c r="K35" s="3">
+        <v>7300</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45473</v>
       </c>
       <c r="G38" s="2">
         <v>45382</v>
@@ -1582,14 +1663,17 @@
       <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
+      <c r="K38" s="2">
+        <v>45107</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1602,8 +1686,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1616,22 +1701,23 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>594000</v>
+      </c>
+      <c r="E41" s="3">
         <v>626400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2500</v>
       </c>
-      <c r="F41" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1500</v>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3">
         <v>600</v>
@@ -1648,8 +1734,11 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1680,22 +1769,25 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E43" s="3">
         <v>49600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12700</v>
       </c>
-      <c r="F43" s="3">
-        <v>11500</v>
-      </c>
-      <c r="G43" s="3">
-        <v>11500</v>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>11500</v>
@@ -1712,8 +1804,11 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1744,19 +1839,22 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E45" s="3">
         <v>6000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6500</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1776,22 +1874,25 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>648500</v>
+      </c>
+      <c r="E46" s="3">
         <v>682100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21700</v>
       </c>
-      <c r="F46" s="3">
-        <v>13100</v>
-      </c>
-      <c r="G46" s="3">
-        <v>13100</v>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3">
         <v>12700</v>
@@ -1808,8 +1909,11 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1840,22 +1944,25 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1375400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1262200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1075800</v>
       </c>
-      <c r="F48" s="3">
-        <v>938500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>938500</v>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
         <v>874600</v>
@@ -1872,22 +1979,25 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>90500</v>
+      </c>
+      <c r="E49" s="3">
         <v>82700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>62900</v>
       </c>
-      <c r="F49" s="3">
-        <v>50700</v>
-      </c>
       <c r="G49" s="3">
-        <v>50700</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>34300</v>
@@ -1904,8 +2014,11 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1936,8 +2049,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1968,22 +2084,25 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6600</v>
       </c>
-      <c r="F52" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2300</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -2000,8 +2119,11 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2032,22 +2154,25 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2120700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2033100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1167100</v>
       </c>
-      <c r="F54" s="3">
-        <v>1004700</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1004700</v>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3">
         <v>921600</v>
@@ -2064,8 +2189,11 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2078,8 +2206,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2092,22 +2221,23 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E57" s="3">
         <v>23700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19600</v>
       </c>
-      <c r="F57" s="3">
-        <v>17200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>17200</v>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
         <v>12000</v>
@@ -2124,8 +2254,11 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2156,17 +2289,20 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E59" s="3">
         <v>26700</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2188,22 +2324,25 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E60" s="3">
         <v>50400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19600</v>
       </c>
-      <c r="F60" s="3">
-        <v>17200</v>
-      </c>
-      <c r="G60" s="3">
-        <v>17200</v>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3">
         <v>12000</v>
@@ -2220,13 +2359,16 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -2252,22 +2394,25 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E62" s="3">
         <v>40100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>30500</v>
       </c>
-      <c r="F62" s="3">
-        <v>22000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>22000</v>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
         <v>21200</v>
@@ -2284,8 +2429,11 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2316,8 +2464,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,8 +2499,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2380,22 +2534,25 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>185200</v>
+      </c>
+      <c r="E66" s="3">
         <v>90500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>50000</v>
       </c>
-      <c r="F66" s="3">
-        <v>39100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>39100</v>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3">
         <v>59000</v>
@@ -2412,8 +2569,11 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2426,8 +2586,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2458,8 +2619,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2490,8 +2654,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2522,8 +2689,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2554,8 +2724,11 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2586,8 +2759,11 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2618,8 +2794,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2650,8 +2829,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2682,22 +2864,25 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1933800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1941800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1117000</v>
       </c>
-      <c r="F76" s="3">
-        <v>965500</v>
-      </c>
       <c r="G76" s="3">
-        <v>965500</v>
+        <v>862600</v>
       </c>
       <c r="H76" s="3">
         <v>862600</v>
@@ -2714,8 +2899,11 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2746,24 +2934,27 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45473</v>
       </c>
       <c r="G80" s="2">
         <v>45382</v>
@@ -2777,28 +2968,31 @@
       <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
+      <c r="K80" s="2">
+        <v>45107</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E81" s="3">
         <v>11500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15400</v>
       </c>
-      <c r="F81" s="3">
-        <v>7100</v>
-      </c>
       <c r="G81" s="3">
-        <v>7100</v>
+        <v>8000</v>
       </c>
       <c r="H81" s="3">
         <v>7600</v>
@@ -2809,14 +3003,17 @@
       <c r="J81" s="3">
         <v>7300</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
+      <c r="K81" s="3">
+        <v>7300</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2829,8 +3026,9 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2861,8 +3059,11 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2893,8 +3094,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2925,8 +3129,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2957,8 +3164,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2989,8 +3199,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3021,22 +3234,25 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E89" s="3">
         <v>29000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7100</v>
       </c>
-      <c r="F89" s="3">
-        <v>16200</v>
-      </c>
       <c r="G89" s="3">
-        <v>16200</v>
+        <v>15500</v>
       </c>
       <c r="H89" s="3">
         <v>10300</v>
@@ -3047,14 +3263,17 @@
       <c r="J89" s="3">
         <v>15800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
+      <c r="K89" s="3">
+        <v>15800</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3067,8 +3286,9 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3099,8 +3319,11 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3131,8 +3354,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3163,22 +3389,25 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-128300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-202700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-153800</v>
       </c>
-      <c r="F94" s="3">
-        <v>-40400</v>
-      </c>
       <c r="G94" s="3">
-        <v>-40400</v>
+        <v>-22800</v>
       </c>
       <c r="H94" s="3">
         <v>-66900</v>
@@ -3189,14 +3418,17 @@
       <c r="J94" s="3">
         <v>-43600</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>-43600</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3209,13 +3441,14 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>3</v>
+      <c r="D96" s="3">
+        <v>26500</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>3</v>
@@ -3241,8 +3474,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3273,8 +3509,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3305,8 +3544,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3337,22 +3579,25 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E100" s="3">
         <v>797600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>161900</v>
       </c>
-      <c r="F100" s="3">
-        <v>24700</v>
-      </c>
       <c r="G100" s="3">
-        <v>24700</v>
+        <v>8200</v>
       </c>
       <c r="H100" s="3">
         <v>56300</v>
@@ -3363,14 +3608,17 @@
       <c r="J100" s="3">
         <v>28000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>28000</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3401,22 +3649,25 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E102" s="3">
         <v>623900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1000</v>
       </c>
-      <c r="F102" s="3">
-        <v>400</v>
-      </c>
       <c r="G102" s="3">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="H102" s="3">
         <v>-400</v>
@@ -3428,9 +3679,12 @@
         <v>200</v>
       </c>
       <c r="K102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CURB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CURB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>CURB</t>
   </si>
@@ -656,172 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45199</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45107</v>
       </c>
       <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
+      <c r="L7" s="2">
+        <v>45107</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E8" s="3">
         <v>38700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>29800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>28200</v>
+      </c>
+      <c r="I8" s="3">
         <v>28000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>25500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>24200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>22000</v>
       </c>
       <c r="K8" s="3">
         <v>22000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
+      <c r="L8" s="3">
+        <v>22000</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E9" s="3">
         <v>10200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>5600</v>
       </c>
       <c r="I9" s="3">
         <v>6000</v>
       </c>
       <c r="J9" s="3">
-        <v>5200</v>
+        <v>5600</v>
       </c>
       <c r="K9" s="3">
         <v>5200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
+      <c r="L9" s="3">
+        <v>5200</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E10" s="3">
         <v>28500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>26200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>22100</v>
+      </c>
+      <c r="J10" s="3">
         <v>19900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>18300</v>
-      </c>
-      <c r="J10" s="3">
-        <v>16800</v>
       </c>
       <c r="K10" s="3">
         <v>16800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
+      <c r="L10" s="3">
+        <v>16800</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,8 +849,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -870,8 +885,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,32 +923,35 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>30800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>23600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>2700</v>
       </c>
-      <c r="I14" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -940,43 +961,49 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E15" s="3">
         <v>14500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>9400</v>
+      </c>
+      <c r="I15" s="3">
         <v>9200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>8800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>7600</v>
       </c>
       <c r="K15" s="3">
         <v>7600</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,78 +1014,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E17" s="3">
         <v>33600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>31100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>17600</v>
+      </c>
+      <c r="I17" s="3">
         <v>16700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>15800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>15100</v>
-      </c>
-      <c r="J17" s="3">
-        <v>13900</v>
       </c>
       <c r="K17" s="3">
         <v>13900</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
+      <c r="L17" s="3">
+        <v>13900</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E18" s="3">
         <v>5100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I18" s="3">
         <v>11300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>9700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>9200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>8000</v>
       </c>
       <c r="K18" s="3">
         <v>8000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
+      <c r="L18" s="3">
+        <v>8000</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,98 +1106,105 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-31100</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>3100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>300</v>
       </c>
       <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>300</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E21" s="3">
         <v>20000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>47100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>19900</v>
+      </c>
+      <c r="I21" s="3">
         <v>17500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>19500</v>
-      </c>
-      <c r="I21" s="3">
-        <v>16800</v>
-      </c>
-      <c r="J21" s="3">
-        <v>15300</v>
       </c>
       <c r="K21" s="3">
         <v>15300</v>
       </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>15300</v>
       </c>
       <c r="M21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E22" s="3">
         <v>600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>400</v>
       </c>
       <c r="J22" s="3">
         <v>400</v>
@@ -1171,49 +1212,55 @@
       <c r="K22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>400</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E23" s="3">
         <v>10700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I23" s="3">
         <v>8000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>7600</v>
-      </c>
-      <c r="I23" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>7300</v>
       </c>
       <c r="K23" s="3">
         <v>7300</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
+      <c r="L23" s="3">
+        <v>7300</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1221,10 +1268,10 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1247,8 +1294,11 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,78 +1332,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E26" s="3">
         <v>10600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I26" s="3">
         <v>8000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>7600</v>
-      </c>
-      <c r="I26" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J26" s="3">
-        <v>7300</v>
       </c>
       <c r="K26" s="3">
         <v>7300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
+      <c r="L26" s="3">
+        <v>7300</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E27" s="3">
         <v>10400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I27" s="3">
         <v>8000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>7600</v>
-      </c>
-      <c r="I27" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J27" s="3">
-        <v>7300</v>
       </c>
       <c r="K27" s="3">
         <v>7300</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
+      <c r="L27" s="3">
+        <v>7300</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1446,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1484,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,78 +1560,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>31100</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-300</v>
       </c>
       <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>-300</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E33" s="3">
         <v>10600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>11500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I33" s="3">
         <v>8000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>7600</v>
-      </c>
-      <c r="I33" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J33" s="3">
-        <v>7300</v>
       </c>
       <c r="K33" s="3">
         <v>7300</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
+      <c r="L33" s="3">
+        <v>7300</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,83 +1674,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E35" s="3">
         <v>10600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>11500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I35" s="3">
         <v>8000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>7600</v>
-      </c>
-      <c r="I35" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J35" s="3">
-        <v>7300</v>
       </c>
       <c r="K35" s="3">
         <v>7300</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
+      <c r="L35" s="3">
+        <v>7300</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45199</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45107</v>
       </c>
       <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
+      <c r="L38" s="2">
+        <v>45107</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,32 +1789,33 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>429900</v>
+      </c>
+      <c r="E41" s="3">
         <v>594000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>626400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2500</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,8 +1825,11 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1772,22 +1863,25 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E43" s="3">
         <v>49500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>49600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12700</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>11500</v>
@@ -1795,8 +1889,8 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3">
+        <v>11500</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1807,8 +1901,11 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1842,32 +1939,35 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E45" s="3">
         <v>4900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6500</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1877,32 +1977,35 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>485100</v>
+      </c>
+      <c r="E46" s="3">
         <v>648500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>682100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21700</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H46" s="3">
+        <v>13100</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3">
         <v>12700</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1912,8 +2015,11 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1947,32 +2053,35 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1519200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1375400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1262200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1075800</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H48" s="3">
+        <v>938500</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>874600</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1982,32 +2091,35 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>101300</v>
+      </c>
+      <c r="E49" s="3">
         <v>90500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>82700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>62900</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
+        <v>50700</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>34300</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,8 +2129,11 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,25 +2205,28 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6600</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+      <c r="H52" s="3">
+        <v>2300</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2122,8 +2243,11 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,32 +2281,35 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2133800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2120700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2033100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1167100</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H54" s="3">
+        <v>1004700</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3">
         <v>921600</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,8 +2319,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,32 +2353,33 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E57" s="3">
         <v>23000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19600</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H57" s="3">
+        <v>17200</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>12000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,8 +2389,11 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2277,11 +2412,11 @@
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2292,20 +2427,23 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E59" s="3">
         <v>17300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26700</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2327,32 +2465,35 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E60" s="3">
         <v>40400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>50400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19600</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H60" s="3">
+        <v>17200</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
         <v>12000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,17 +2503,20 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>99100</v>
+      </c>
+      <c r="E61" s="3">
         <v>99000</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -2380,14 +2524,14 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>25800</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2397,32 +2541,35 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E62" s="3">
         <v>45800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>40100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>30500</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3">
+        <v>22000</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>21200</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2432,8 +2579,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,32 +2693,35 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>204800</v>
+      </c>
+      <c r="E66" s="3">
         <v>185200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>90500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>50000</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H66" s="3">
+        <v>39100</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3">
         <v>59000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,8 +2731,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2692,8 +2861,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,8 +2899,11 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2762,8 +2937,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,32 +3051,35 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1926200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1933800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1941800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1117000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>965500</v>
+      </c>
+      <c r="I76" s="3">
         <v>862600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>862600</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2902,8 +3089,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,83 +3127,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45199</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45107</v>
       </c>
       <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
+      <c r="L80" s="2">
+        <v>45107</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E81" s="3">
         <v>10600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>11500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I81" s="3">
         <v>8000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>7600</v>
-      </c>
-      <c r="I81" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J81" s="3">
-        <v>7300</v>
       </c>
       <c r="K81" s="3">
         <v>7300</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
+      <c r="L81" s="3">
+        <v>7300</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,29 +3226,30 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>8000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>7600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>7600</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3062,8 +3262,11 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,43 +3452,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E89" s="3">
         <v>25400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>29000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>16900</v>
+      </c>
+      <c r="I89" s="3">
         <v>15500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>10300</v>
-      </c>
-      <c r="I89" s="3">
-        <v>17400</v>
-      </c>
-      <c r="J89" s="3">
-        <v>15800</v>
       </c>
       <c r="K89" s="3">
         <v>15800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
+      <c r="L89" s="3">
+        <v>15800</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,8 +3508,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3322,8 +3544,11 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,43 +3620,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-180200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-128300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-202700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-153800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-58100</v>
+      </c>
+      <c r="I94" s="3">
         <v>-22800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-66900</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-31900</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-43600</v>
       </c>
       <c r="K94" s="3">
         <v>-43600</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3">
+        <v>-43600</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,17 +3676,18 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E96" s="3">
         <v>26500</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F96" s="3" t="s">
         <v>3</v>
       </c>
@@ -3477,8 +3712,11 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,43 +3826,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E100" s="3">
         <v>70500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>797600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>161900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>41100</v>
+      </c>
+      <c r="I100" s="3">
         <v>8200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>56300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>14600</v>
-      </c>
-      <c r="J100" s="3">
-        <v>28000</v>
       </c>
       <c r="K100" s="3">
         <v>28000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="3">
+        <v>28000</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3652,39 +3902,45 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-164200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-32400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>623900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>200</v>
       </c>
       <c r="K102" s="3">
         <v>200</v>
       </c>
       <c r="L102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CURB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CURB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
   <si>
     <t>CURB</t>
   </si>
@@ -656,199 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45107</v>
       </c>
       <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
+      <c r="N7" s="2">
+        <v>45107</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>54100</v>
+      </c>
+      <c r="E8" s="3">
         <v>48600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>41400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>38700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>34900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>29800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>28200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>28000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25500</v>
-      </c>
-      <c r="L8" s="3">
-        <v>22000</v>
       </c>
       <c r="M8" s="3">
         <v>22000</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
+      <c r="N8" s="3">
+        <v>22000</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E9" s="3">
         <v>12600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6900</v>
-      </c>
-      <c r="I9" s="3">
-        <v>6000</v>
       </c>
       <c r="J9" s="3">
         <v>6000</v>
       </c>
       <c r="K9" s="3">
+        <v>6000</v>
+      </c>
+      <c r="L9" s="3">
         <v>5600</v>
-      </c>
-      <c r="L9" s="3">
-        <v>5200</v>
       </c>
       <c r="M9" s="3">
         <v>5200</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
+      <c r="N9" s="3">
+        <v>5200</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E10" s="3">
         <v>36000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>28500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>22100</v>
       </c>
       <c r="J10" s="3">
         <v>22100</v>
       </c>
       <c r="K10" s="3">
+        <v>22100</v>
+      </c>
+      <c r="L10" s="3">
         <v>19900</v>
-      </c>
-      <c r="L10" s="3">
-        <v>16800</v>
       </c>
       <c r="M10" s="3">
         <v>16800</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
+      <c r="N10" s="3">
+        <v>16800</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +876,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +918,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,38 +962,41 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-1300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>30800</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I14" s="3">
         <v>23600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>2700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,49 +1006,55 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E15" s="3">
         <v>19800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>7600</v>
       </c>
       <c r="M15" s="3">
         <v>7600</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1067,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E17" s="3">
         <v>39700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>33600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>31100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15800</v>
-      </c>
-      <c r="L17" s="3">
-        <v>13900</v>
       </c>
       <c r="M17" s="3">
         <v>13900</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
+      <c r="N17" s="3">
+        <v>13900</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E18" s="3">
         <v>9000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9700</v>
-      </c>
-      <c r="L18" s="3">
-        <v>8000</v>
       </c>
       <c r="M18" s="3">
         <v>8000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
+      <c r="N18" s="3">
+        <v>8000</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,116 +1173,123 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
-        <v>-31100</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>-200</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>3100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>300</v>
       </c>
       <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>300</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E21" s="3">
         <v>29100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>22700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>20000</v>
       </c>
-      <c r="G21" s="3">
-        <v>47100</v>
-      </c>
       <c r="H21" s="3">
+        <v>16300</v>
+      </c>
+      <c r="I21" s="3">
         <v>19300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>17500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19500</v>
-      </c>
-      <c r="L21" s="3">
-        <v>15300</v>
       </c>
       <c r="M21" s="3">
         <v>15300</v>
       </c>
       <c r="N21" s="3">
-        <v>0</v>
+        <v>15300</v>
       </c>
       <c r="O21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E22" s="3">
         <v>4000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>400</v>
       </c>
       <c r="L22" s="3">
         <v>400</v>
@@ -1258,72 +1297,78 @@
       <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>400</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E23" s="3">
         <v>9400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7600</v>
-      </c>
-      <c r="L23" s="3">
-        <v>7300</v>
       </c>
       <c r="M23" s="3">
         <v>7300</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
+      <c r="N23" s="3">
+        <v>7300</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1346,8 +1391,11 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1435,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E26" s="3">
         <v>9400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7600</v>
-      </c>
-      <c r="L26" s="3">
-        <v>7300</v>
       </c>
       <c r="M26" s="3">
         <v>7300</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
+      <c r="N26" s="3">
+        <v>7300</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E27" s="3">
         <v>9200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-15400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7600</v>
-      </c>
-      <c r="L27" s="3">
-        <v>7300</v>
       </c>
       <c r="M27" s="3">
         <v>7300</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
+      <c r="N27" s="3">
+        <v>7300</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1567,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1611,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1655,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1699,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
-        <v>31100</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>200</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-300</v>
       </c>
       <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>-300</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E33" s="3">
         <v>9300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-15400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7600</v>
-      </c>
-      <c r="L33" s="3">
-        <v>7300</v>
       </c>
       <c r="M33" s="3">
         <v>7300</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
+      <c r="N33" s="3">
+        <v>7300</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1831,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E35" s="3">
         <v>9300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-15400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7600</v>
-      </c>
-      <c r="L35" s="3">
-        <v>7300</v>
       </c>
       <c r="M35" s="3">
         <v>7300</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
+      <c r="N35" s="3">
+        <v>7300</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
-      </c>
-      <c r="L38" s="2">
-        <v>45107</v>
       </c>
       <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
+      <c r="N38" s="2">
+        <v>45107</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1944,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,38 +1962,39 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>289600</v>
+      </c>
+      <c r="E41" s="3">
         <v>430100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>429900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>594000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>626400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1500</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3">
         <v>600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,8 +2004,11 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1936,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -1959,38 +2048,41 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E43" s="3">
         <v>49400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>50100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>49500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>49600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>11500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2000,8 +2092,11 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2041,38 +2136,41 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E45" s="3">
         <v>3600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4900</v>
       </c>
-      <c r="G45" s="3">
-        <v>6000</v>
-      </c>
       <c r="H45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I45" s="3">
         <v>6500</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2082,38 +2180,41 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>336100</v>
+      </c>
+      <c r="E46" s="3">
         <v>483100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>485100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>648500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>682100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3">
         <v>12700</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,8 +2224,11 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2164,38 +2268,41 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1988500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1823500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1519200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1375400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1262200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1075800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>938500</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3">
         <v>874600</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2205,38 +2312,41 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>137500</v>
+      </c>
+      <c r="E49" s="3">
         <v>129400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>101300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>90500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>82700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>62900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>50700</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>34300</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2246,8 +2356,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2400,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,32 +2444,35 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E52" s="3">
         <v>6200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2300</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2369,8 +2488,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,38 +2532,41 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2469800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2445300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2133800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2120700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2033100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1167100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1004700</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3">
         <v>921600</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2451,8 +2576,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2596,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,38 +2614,39 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E57" s="3">
         <v>44300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>32500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17200</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>12000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2526,13 +2656,16 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2555,8 +2688,8 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2567,8 +2700,11 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2576,17 +2712,17 @@
         <v>20900</v>
       </c>
       <c r="E59" s="3">
+        <v>20900</v>
+      </c>
+      <c r="F59" s="3">
         <v>20400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26700</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2608,38 +2744,41 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>66400</v>
+      </c>
+      <c r="E60" s="3">
         <v>65500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>40400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>50400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17200</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3">
         <v>12000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,23 +2788,26 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>423200</v>
+      </c>
+      <c r="E61" s="3">
         <v>396400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>99100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>99000</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2676,11 +2818,11 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>25800</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2690,38 +2832,41 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E62" s="3">
         <v>59800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>52500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>45800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>40100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>30500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>21200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2731,8 +2876,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2920,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2964,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,38 +3008,41 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>556300</v>
+      </c>
+      <c r="E66" s="3">
         <v>521800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>204800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>185200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>90500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>39100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3">
         <v>59000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,8 +3052,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3072,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3114,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3158,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3202,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,8 +3246,11 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3117,8 +3290,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3334,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3378,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,37 +3422,40 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1909200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1920000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1926200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1933800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1941800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1117000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>965500</v>
-      </c>
-      <c r="J76" s="3">
-        <v>862600</v>
       </c>
       <c r="K76" s="3">
         <v>862600</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
+      <c r="L76" s="3">
+        <v>862600</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
@@ -3281,8 +3466,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3510,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45107</v>
       </c>
       <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
+      <c r="N80" s="2">
+        <v>45107</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E81" s="3">
         <v>9300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-15400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7600</v>
-      </c>
-      <c r="L81" s="3">
-        <v>7300</v>
       </c>
       <c r="M81" s="3">
         <v>7300</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
+      <c r="N81" s="3">
+        <v>7300</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,34 +3623,35 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E83" s="3">
         <v>8400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>7600</v>
       </c>
       <c r="J83" s="3">
         <v>7600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>7600</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3467,8 +3665,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3709,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3753,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3797,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3841,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3885,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E89" s="3">
         <v>39200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>34200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>25400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>29000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>16900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10300</v>
-      </c>
-      <c r="L89" s="3">
-        <v>15800</v>
       </c>
       <c r="M89" s="3">
         <v>15800</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="N89" s="3">
+        <v>15800</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +3949,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3771,8 +3991,11 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4035,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4079,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-175000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-319800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-180200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-128300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-202700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-153800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-58100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-66900</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-43600</v>
       </c>
       <c r="M94" s="3">
         <v>-43600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>-43600</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,8 +4143,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3923,11 +4156,11 @@
         <v>17000</v>
       </c>
       <c r="F96" s="3">
+        <v>17000</v>
+      </c>
+      <c r="G96" s="3">
         <v>26500</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>3</v>
       </c>
@@ -3952,8 +4185,11 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4229,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4273,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,49 +4317,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E100" s="3">
         <v>280900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>70500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>797600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>161900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>41100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>56300</v>
-      </c>
-      <c r="L100" s="3">
-        <v>28000</v>
       </c>
       <c r="M100" s="3">
         <v>28000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>28000</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4157,45 +4405,51 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-140600</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-164200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-32400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>623900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
-      </c>
-      <c r="L102" s="3">
-        <v>200</v>
       </c>
       <c r="M102" s="3">
         <v>200</v>
       </c>
       <c r="N102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CURB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CURB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>CURB</t>
   </si>
@@ -656,211 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
-      </c>
-      <c r="M7" s="2">
-        <v>45107</v>
       </c>
       <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
+      <c r="O7" s="2">
+        <v>45107</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E8" s="3">
         <v>54100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>48600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>34900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>29800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>28200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>28000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>25500</v>
-      </c>
-      <c r="M8" s="3">
-        <v>22000</v>
       </c>
       <c r="N8" s="3">
         <v>22000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
+      <c r="O8" s="3">
+        <v>22000</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E9" s="3">
         <v>12400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6900</v>
-      </c>
-      <c r="J9" s="3">
-        <v>6000</v>
       </c>
       <c r="K9" s="3">
         <v>6000</v>
       </c>
       <c r="L9" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M9" s="3">
         <v>5600</v>
-      </c>
-      <c r="M9" s="3">
-        <v>5200</v>
       </c>
       <c r="N9" s="3">
         <v>5200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
+      <c r="O9" s="3">
+        <v>5200</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E10" s="3">
         <v>41700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>36000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>30800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>28500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>26200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22900</v>
-      </c>
-      <c r="J10" s="3">
-        <v>22100</v>
       </c>
       <c r="K10" s="3">
         <v>22100</v>
       </c>
       <c r="L10" s="3">
+        <v>22100</v>
+      </c>
+      <c r="M10" s="3">
         <v>19900</v>
-      </c>
-      <c r="M10" s="3">
-        <v>16800</v>
       </c>
       <c r="N10" s="3">
         <v>16800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3">
+        <v>16800</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,8 +890,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -921,8 +935,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,41 +982,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>23600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>2700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,52 +1029,58 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E15" s="3">
         <v>22100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>7600</v>
       </c>
       <c r="N15" s="3">
         <v>7600</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,96 +1094,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E17" s="3">
         <v>44100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>39700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15800</v>
-      </c>
-      <c r="M17" s="3">
-        <v>13900</v>
       </c>
       <c r="N17" s="3">
         <v>13900</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
+      <c r="O17" s="3">
+        <v>13900</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E18" s="3">
         <v>10000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9700</v>
-      </c>
-      <c r="M18" s="3">
-        <v>8000</v>
       </c>
       <c r="N18" s="3">
         <v>8000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
+      <c r="O18" s="3">
+        <v>8000</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,125 +1207,132 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>3100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>300</v>
       </c>
       <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>300</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E21" s="3">
         <v>33000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>29100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>22700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>20000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>17500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19500</v>
-      </c>
-      <c r="M21" s="3">
-        <v>15300</v>
       </c>
       <c r="N21" s="3">
         <v>15300</v>
       </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>15300</v>
       </c>
       <c r="P21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E22" s="3">
         <v>5800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>400</v>
       </c>
       <c r="M22" s="3">
         <v>400</v>
@@ -1300,58 +1340,64 @@
       <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>400</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E23" s="3">
         <v>9600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7600</v>
-      </c>
-      <c r="M23" s="3">
-        <v>7300</v>
       </c>
       <c r="N23" s="3">
         <v>7300</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
+      <c r="O23" s="3">
+        <v>7300</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1359,19 +1405,19 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1394,8 +1440,11 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1438,96 +1487,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E26" s="3">
         <v>9600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7600</v>
-      </c>
-      <c r="M26" s="3">
-        <v>7300</v>
       </c>
       <c r="N26" s="3">
         <v>7300</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
+      <c r="O26" s="3">
+        <v>7300</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E27" s="3">
         <v>9400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7600</v>
-      </c>
-      <c r="M27" s="3">
-        <v>7300</v>
       </c>
       <c r="N27" s="3">
         <v>7300</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
+      <c r="O27" s="3">
+        <v>7300</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1570,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1658,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1702,96 +1769,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-3100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-300</v>
       </c>
       <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>-300</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E33" s="3">
         <v>9500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7600</v>
-      </c>
-      <c r="M33" s="3">
-        <v>7300</v>
       </c>
       <c r="N33" s="3">
         <v>7300</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
+      <c r="O33" s="3">
+        <v>7300</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1834,101 +1910,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E35" s="3">
         <v>9500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7600</v>
-      </c>
-      <c r="M35" s="3">
-        <v>7300</v>
       </c>
       <c r="N35" s="3">
         <v>7300</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
+      <c r="O35" s="3">
+        <v>7300</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
-      </c>
-      <c r="M38" s="2">
-        <v>45107</v>
       </c>
       <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
+      <c r="O38" s="2">
+        <v>45107</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1945,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1963,41 +2049,42 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>305800</v>
+      </c>
+      <c r="E41" s="3">
         <v>289600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>430100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>429900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>594000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>626400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3">
         <v>600</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2007,8 +2094,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2025,11 +2115,11 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>1200</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2051,41 +2141,44 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E43" s="3">
         <v>44000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>49400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>50100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>49500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>49600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11500</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
         <v>11500</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,8 +2188,11 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2139,41 +2235,44 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E45" s="3">
         <v>2600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6500</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2183,41 +2282,44 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>350900</v>
+      </c>
+      <c r="E46" s="3">
         <v>336100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>483100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>485100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>648500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>682100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3">
         <v>12700</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2227,8 +2329,11 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2271,41 +2376,44 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2115800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1988500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1823500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1519200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1375400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1262200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1075800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>938500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3">
         <v>874600</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2315,41 +2423,44 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E49" s="3">
         <v>137500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>129400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>101300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>90500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>82700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>62900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>50700</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>34300</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2359,8 +2470,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2447,35 +2564,38 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E52" s="3">
         <v>4900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2300</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2491,8 +2611,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2535,41 +2658,44 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2621100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2469800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2445300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2133800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2120700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2033100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1167100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1004700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3">
         <v>921600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2579,8 +2705,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2597,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2615,41 +2745,42 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E57" s="3">
         <v>42700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>12000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2659,13 +2790,16 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2691,8 +2825,8 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -2703,29 +2837,32 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>20900</v>
+        <v>18900</v>
       </c>
       <c r="E59" s="3">
         <v>20900</v>
       </c>
       <c r="F59" s="3">
+        <v>20900</v>
+      </c>
+      <c r="G59" s="3">
         <v>20400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26700</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2747,41 +2884,44 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>66400</v>
+        <v>57600</v>
       </c>
       <c r="E60" s="3">
+        <v>63600</v>
+      </c>
+      <c r="F60" s="3">
         <v>65500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>40400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>50400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17200</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3">
         <v>12000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,26 +2931,29 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>423200</v>
+        <v>596600</v>
       </c>
       <c r="E61" s="3">
+        <v>426000</v>
+      </c>
+      <c r="F61" s="3">
         <v>396400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>99100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>99000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2821,11 +2964,11 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>25800</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2835,41 +2978,44 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E62" s="3">
         <v>66700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>59800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>52500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>45800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>40100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>30500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>21200</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2879,8 +3025,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2923,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3011,41 +3166,44 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>721800</v>
+      </c>
+      <c r="E66" s="3">
         <v>556300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>521800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>204800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>185200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>90500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>50000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>39100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3">
         <v>59000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3055,8 +3213,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3073,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3117,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3161,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3205,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3249,8 +3420,11 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3293,8 +3467,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3337,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3381,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3425,40 +3608,43 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1894200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1909200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1920000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1926200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1933800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1941800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1117000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>965500</v>
-      </c>
-      <c r="K76" s="3">
-        <v>862600</v>
       </c>
       <c r="L76" s="3">
         <v>862600</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
+      <c r="M76" s="3">
+        <v>862600</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
@@ -3469,8 +3655,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3513,101 +3702,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
-      </c>
-      <c r="M80" s="2">
-        <v>45107</v>
       </c>
       <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
+      <c r="O80" s="2">
+        <v>45107</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E81" s="3">
         <v>9500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7600</v>
-      </c>
-      <c r="M81" s="3">
-        <v>7300</v>
       </c>
       <c r="N81" s="3">
         <v>7300</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
+      <c r="O81" s="3">
+        <v>7300</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3624,37 +3822,38 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E83" s="3">
         <v>8500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>7600</v>
       </c>
       <c r="K83" s="3">
         <v>7600</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>7600</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -3668,8 +3867,11 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3712,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3756,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3800,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3844,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3888,52 +4102,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E89" s="3">
         <v>25900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>39200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>34200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>25400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>29000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10300</v>
-      </c>
-      <c r="M89" s="3">
-        <v>15800</v>
       </c>
       <c r="N89" s="3">
         <v>15800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
+      <c r="O89" s="3">
+        <v>15800</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3950,8 +4170,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3994,8 +4215,11 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4038,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4082,52 +4309,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-152700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-175000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-319800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-180200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-128300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-202700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-153800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-58100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-66900</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-43600</v>
       </c>
       <c r="N94" s="3">
         <v>-43600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>-43600</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4144,13 +4377,14 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>17000</v>
+        <v>20100</v>
       </c>
       <c r="E96" s="3">
         <v>17000</v>
@@ -4159,11 +4393,11 @@
         <v>17000</v>
       </c>
       <c r="G96" s="3">
+        <v>17000</v>
+      </c>
+      <c r="H96" s="3">
         <v>26500</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>3</v>
       </c>
@@ -4188,8 +4422,11 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4232,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4276,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4320,52 +4563,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>147600</v>
+      </c>
+      <c r="E100" s="3">
         <v>8500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>280900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>70500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>797600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>161900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>41100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>56300</v>
-      </c>
-      <c r="M100" s="3">
-        <v>28000</v>
       </c>
       <c r="N100" s="3">
         <v>28000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>28000</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4408,48 +4657,54 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-140600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-164200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-32400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>623900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
-      </c>
-      <c r="M102" s="3">
-        <v>200</v>
       </c>
       <c r="N102" s="3">
         <v>200</v>
       </c>
       <c r="O102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>0</v>
       </c>
     </row>
